--- a/categories_index_removed.xlsx
+++ b/categories_index_removed.xlsx
@@ -8300,7 +8300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -8808,6 +8808,13 @@
       <c r="A70" t="inlineStr">
         <is>
           <t>6810 Bank Charges</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>61500 Bank Fees &amp; Service Charges</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -12767,6 +12774,20 @@
       <c r="A30" t="inlineStr">
         <is>
           <t>6975 Profit Sharing Expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>60002 Officer Bonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>60004 Officer Commissions</t>
         </is>
       </c>
     </row>

--- a/categories_index_removed.xlsx
+++ b/categories_index_removed.xlsx
@@ -4,44 +4,55 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" tabRatio="600" autoFilterDateGrouping="true"/>
   </bookViews>
   <sheets>
-    <sheet name="cash_bank" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="accounts_receivable" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="fixed_assets" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="depreciation_amortization" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="accounts_payable" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="credit_cards" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="payroll_liabilities" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="payroll_benefits" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="deferred_revenue" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="equity" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="loans_liabilities" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="accrued_liabilities" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="income_revenue" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="cogs" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="advertising_marketing" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="auto_expenses" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="bank_fees" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="meals_entertainment" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="travel" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="office_supplies" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="repairs_maintenance" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="taxes_licenses" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="interest_expense" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="bonuses_commissions" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="consulting_legal_it" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="general_expenses" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="misc" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="cash_bank" sheetId="1" r:id="rId1" state="visible"/>
+    <sheet name="accounts_receivable" sheetId="2" r:id="rId2" state="visible"/>
+    <sheet name="fixed_assets" sheetId="3" r:id="rId3" state="visible"/>
+    <sheet name="depreciation_amortization" sheetId="4" r:id="rId4" state="visible"/>
+    <sheet name="accounts_payable" sheetId="5" r:id="rId5" state="visible"/>
+    <sheet name="credit_cards" sheetId="6" r:id="rId6" state="visible"/>
+    <sheet name="payroll_liabilities" sheetId="7" r:id="rId7" state="visible"/>
+    <sheet name="payroll_benefits" sheetId="8" r:id="rId8" state="visible"/>
+    <sheet name="deferred_revenue" sheetId="9" r:id="rId9" state="visible"/>
+    <sheet name="equity" sheetId="10" r:id="rId10" state="visible"/>
+    <sheet name="loans_liabilities" sheetId="11" r:id="rId11" state="visible"/>
+    <sheet name="accrued_liabilities" sheetId="12" r:id="rId12" state="visible"/>
+    <sheet name="income_revenue" sheetId="13" r:id="rId13" state="visible"/>
+    <sheet name="cogs" sheetId="14" r:id="rId14" state="visible"/>
+    <sheet name="advertising_marketing" sheetId="15" r:id="rId15" state="visible"/>
+    <sheet name="auto_expenses" sheetId="16" r:id="rId16" state="visible"/>
+    <sheet name="bank_fees" sheetId="17" r:id="rId17" state="visible"/>
+    <sheet name="meals_entertainment" sheetId="18" r:id="rId18" state="visible"/>
+    <sheet name="travel" sheetId="19" r:id="rId19" state="visible"/>
+    <sheet name="office_supplies" sheetId="20" r:id="rId20" state="visible"/>
+    <sheet name="repairs_maintenance" sheetId="21" r:id="rId21" state="visible"/>
+    <sheet name="taxes_licenses" sheetId="22" r:id="rId22" state="visible"/>
+    <sheet name="interest_expense" sheetId="23" r:id="rId23" state="visible"/>
+    <sheet name="bonuses_commissions" sheetId="24" r:id="rId24" state="visible"/>
+    <sheet name="consulting_legal_it" sheetId="25" r:id="rId25" state="visible"/>
+    <sheet name="general_expenses" sheetId="26" r:id="rId26" state="visible"/>
+    <sheet name="misc" sheetId="27" r:id="rId27" state="visible"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+  <si>
+    <t>6024 Employee Reimbursement</t>
+  </si>
+  <si>
+    <t>7001 Cash Reward</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <numFmts count="0"/>
   <fonts count="2">
     <font>
@@ -82,13 +93,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="false" pivotButton="false"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" quotePrefix="false" pivotButton="false"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="false"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -161,7 +172,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -13123,15 +13134,15 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13833,6 +13844,11 @@
         <is>
           <t>8800 Other Miscellaneous Expense</t>
         </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -19205,15 +19221,15 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20370,6 +20386,11 @@
         <is>
           <t>7004 Credit Card Rewards</t>
         </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/categories_index_removed.xlsx
+++ b/categories_index_removed.xlsx
@@ -455,15 +455,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1873,15 +1873,15 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3060,15 +3060,15 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4408,15 +4408,15 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5273,15 +5273,15 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6537,15 +6537,15 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7350,292 +7350,278 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>5150 Direct Labor - Bonus</t>
+          <t>51700 Media Purchased for Clients</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>5150 Direct Labor - Bonuses</t>
+          <t>5180 Direct Labor - Worker's Comp</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>51700 Media Purchased for Clients</t>
+          <t>5200 Direct Purchases</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>5180 Direct Labor - Worker's Comp</t>
+          <t>5200 Freight &amp; Courier</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>5200 Direct Purchases</t>
+          <t>5200 Inbound Freight</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>5200 Freight &amp; Courier</t>
+          <t>5200 Reimbursed Client Expenses</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>5200 Inbound Freight</t>
+          <t>5200 Shipping, Freight &amp; Delivery</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>5200 Reimbursed Client Expenses</t>
+          <t>52000 Cost of Post-Production</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>5200 Shipping, Freight &amp; Delivery</t>
+          <t>5210 Call Rail Fees</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>52000 Cost of Post-Production</t>
+          <t>5220 Twilio Fees</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>5210 Call Rail Fees</t>
+          <t>5230 NexHealth Fees</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>5220 Twilio Fees</t>
+          <t>5300 Outbound Freight</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5230 NexHealth Fees</t>
+          <t>5300 People Costs - Direct</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>5300 Outbound Freight</t>
+          <t>53000 Cost of Production</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>5300 People Costs - Direct</t>
+          <t>53002 Direct Production Costs</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>53000 Cost of Production</t>
+          <t>53003 Supplies &amp; Parts</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>53002 Direct Production Costs</t>
+          <t>5310 Parts</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>53003 Supplies &amp; Parts</t>
+          <t>5400 Project Costs</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>5310 Parts</t>
+          <t>5400 Raw Materials</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>5400 Project Costs</t>
+          <t>5400 Supplies &amp; Materials</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>5400 Raw Materials</t>
+          <t>54000 Direct Contract Labor</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>5400 Supplies &amp; Materials</t>
+          <t>54001 Pier 32 Marina</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>54000 Direct Contract Labor</t>
+          <t>54002 Point Loma</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>54001 Pier 32 Marina</t>
+          <t>5410 COGS-Event/Project Manage...</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>54002 Point Loma</t>
+          <t>5435 COGS-Marketing Consulting</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>5410 COGS-Event/Project Manage...</t>
+          <t>5445 COGS-PR Consulting</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5435 COGS-Marketing Consulting</t>
+          <t>5450 COGS-Copywriting</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>5445 COGS-PR Consulting</t>
+          <t>5500 Client Expenses &amp; Supplies</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>5450 COGS-Copywriting</t>
+          <t>55000 Direct Labor</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>5500 Client Expenses &amp; Supplies</t>
+          <t>5509 Royalties on Acquisition</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>55000 Direct Labor</t>
+          <t>5510 Client Supplies (Non Reim...</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5509 Royalties on Acquisition</t>
+          <t>5515 Media Clippings</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>5510 Client Supplies (Non Reim...</t>
+          <t>56000 Pass-through - Expenses</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5515 Media Clippings</t>
+          <t>60002 Contract Labor</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>56000 Pass-through - Expenses</t>
+          <t>6001 Contract Labor</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>60002 Contract Labor</t>
+          <t>60104-000 Marketing Materials</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>6001 Contract Labor</t>
+          <t>6100 Indirect Labor - Employees</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>60104-000 Marketing Materials</t>
+          <t>6300 Program Expenses</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>6100 Indirect Labor - Employees</t>
+          <t>64800 Subcontractors</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
-        <is>
-          <t>6300 Program Expenses</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>64800 Subcontractors</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
         <is>
           <t>6750 Subcontractor Expense</t>
         </is>
@@ -7647,15 +7633,15 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7980,15 +7966,15 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8306,15 +8292,15 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8835,15 +8821,15 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9140,15 +9126,15 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9690,15 +9676,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11185,15 +11171,15 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11658,15 +11644,15 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11942,15 +11928,15 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12261,15 +12247,15 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12552,15 +12538,15 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12588,215 +12574,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1-65520 Bonuses</t>
+          <t>2402 Accrued Commission Payable</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2401 Accrued Bonuses</t>
+          <t>2506 Commission Advance</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2402 Accrued Commission Payable</t>
+          <t>4001 Buyer Commission</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2506 Commission Advance</t>
+          <t>4002 Lease Commission</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3-65520 Bonuses</t>
+          <t>4003 Listing Commission</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4001 Buyer Commission</t>
+          <t>4004 Referral Commission</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4002 Lease Commission</t>
+          <t>6103 Employee PR - Commission</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4003 Listing Commission</t>
+          <t>6254 Commission Fees - NowCorp</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4004 Referral Commission</t>
+          <t>6975 Profit Sharing Expense</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
-        <is>
-          <t>5023 DL - Bonus</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>60005 Bonus</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>60006 Bonus</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>6004 Employee Bonus</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>60040 Bonus</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>60050 Bonus</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>6009 Bonus</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>6023 Employee Bonus</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>6024 Employee PR - Bonuses</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>6025 Employee Bonuses</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>6103 Employee PR - Commission</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>6111 Employee PR - Bonus</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>6254 Commission Fees - NowCorp</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>6359 Margin Bonus</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>6361 Bonus &amp; Incentives</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>6404 Employee Bonus</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>64500 Bonus</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>6555 Bonus</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>6709 Bonus</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>6975 Profit Sharing Expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>60002 Officer Bonus</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
         <is>
           <t>60004 Officer Commissions</t>
         </is>
@@ -12808,15 +12647,15 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13857,15 +13696,15 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16535,15 +16374,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18926,15 +18765,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19063,15 +18902,15 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20399,15 +20238,15 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21096,15 +20935,15 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21520,15 +21359,15 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
